--- a/Versão5/SUS/Ontologia_RDC_50.xlsx
+++ b/Versão5/SUS/Ontologia_RDC_50.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\RDC5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01B8E2A-EADE-4EE4-8898-881D8D8C625E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EF7683-DAE6-49B8-B67C-54591DD0F33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -3592,14 +3592,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -3638,6 +3630,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3981,15 +3981,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="93.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="93.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>45</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>47</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>48</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>49</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>50</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>51</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>52</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>54</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>55</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>57</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>59</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>60</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>61</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>62</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>63</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>64</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>65</v>
       </c>
@@ -4178,19 +4178,19 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46244.652840509261</v>
+        <v>46249.448083564814</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>67</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>68</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>90</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
         <v>89</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>91</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>69</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>70</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="17" t="s">
         <v>84</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="15" t="s">
         <v>93</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="15" t="s">
         <v>95</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
         <v>97</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>99</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>101</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>103</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>105</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>107</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>109</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>111</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>113</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="17" t="s">
         <v>115</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>117</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>119</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="59" t="s">
         <v>771</v>
       </c>
@@ -4465,35 +4465,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="1.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.53515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.23046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.3046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>44</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>Primary activity defined by RDC50</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38">
         <v>3</v>
       </c>
@@ -4763,34 +4763,34 @@
     <sortCondition ref="A1:A2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="V2 A2:A3">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:A3 S2:V3">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1">
-    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="64" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3 M2:Q3">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="duplicateValues" dxfId="5" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="4" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:U2 AA2:XFD3 S3:V3">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+  <conditionalFormatting sqref="AA2:XFD3">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4806,19 +4806,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -4951,7 +4951,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4967,14 +4967,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -4998,7 +4998,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5009,76 +5009,76 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5247C9F-0832-49D6-8CCC-8F4A7A71BCAA}">
   <dimension ref="A1:BM332"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" customWidth="1"/>
+    <col min="2" max="2" width="5.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.84375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.69140625" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="7" max="7" width="5.69140625" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.69140625" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.69140625" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.69140625" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="5.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.69140625" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="5.69140625" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" customWidth="1"/>
+    <col min="19" max="19" width="5.69140625" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="5.69140625" customWidth="1"/>
     <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="23" width="5.7109375" customWidth="1"/>
+    <col min="23" max="23" width="5.69140625" customWidth="1"/>
     <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="25" width="5.7109375" customWidth="1"/>
+    <col min="25" max="25" width="5.69140625" customWidth="1"/>
     <col min="26" max="26" width="8" customWidth="1"/>
-    <col min="27" max="27" width="5.7109375" customWidth="1"/>
+    <col min="27" max="27" width="5.69140625" customWidth="1"/>
     <col min="28" max="28" width="8" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" customWidth="1"/>
+    <col min="29" max="29" width="5.69140625" customWidth="1"/>
     <col min="30" max="30" width="8" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
+    <col min="31" max="31" width="5.69140625" customWidth="1"/>
     <col min="32" max="32" width="8" customWidth="1"/>
-    <col min="33" max="33" width="5.7109375" customWidth="1"/>
+    <col min="33" max="33" width="5.69140625" customWidth="1"/>
     <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="35" width="5.7109375" customWidth="1"/>
+    <col min="35" max="35" width="5.69140625" customWidth="1"/>
     <col min="36" max="36" width="8" customWidth="1"/>
-    <col min="37" max="37" width="5.7109375" customWidth="1"/>
+    <col min="37" max="37" width="5.69140625" customWidth="1"/>
     <col min="38" max="38" width="8" customWidth="1"/>
-    <col min="39" max="39" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="5.69140625" customWidth="1"/>
     <col min="40" max="40" width="8" customWidth="1"/>
-    <col min="41" max="41" width="5.7109375" customWidth="1"/>
+    <col min="41" max="41" width="5.69140625" customWidth="1"/>
     <col min="42" max="42" width="8" customWidth="1"/>
-    <col min="43" max="43" width="5.7109375" customWidth="1"/>
+    <col min="43" max="43" width="5.69140625" customWidth="1"/>
     <col min="44" max="44" width="8" customWidth="1"/>
-    <col min="45" max="45" width="5.7109375" customWidth="1"/>
+    <col min="45" max="45" width="5.69140625" customWidth="1"/>
     <col min="46" max="46" width="8" customWidth="1"/>
-    <col min="47" max="47" width="5.7109375" customWidth="1"/>
+    <col min="47" max="47" width="5.69140625" customWidth="1"/>
     <col min="48" max="48" width="8" customWidth="1"/>
-    <col min="49" max="49" width="5.7109375" customWidth="1"/>
+    <col min="49" max="49" width="5.69140625" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
-    <col min="51" max="51" width="4.7109375" customWidth="1"/>
-    <col min="52" max="52" width="3.140625" customWidth="1"/>
-    <col min="53" max="53" width="19.5703125" customWidth="1"/>
-    <col min="54" max="54" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="103.140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="4.69140625" customWidth="1"/>
+    <col min="52" max="52" width="3.15234375" customWidth="1"/>
+    <col min="53" max="53" width="19.53515625" customWidth="1"/>
+    <col min="54" max="54" width="4.15234375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="103.15234375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="2.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -11776,7 +11776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -13549,7 +13549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -13746,7 +13746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -13943,7 +13943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -14337,7 +14337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -14731,7 +14731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -15519,7 +15519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -15716,7 +15716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -16898,7 +16898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -17686,7 +17686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -17883,7 +17883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -18080,7 +18080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -18671,7 +18671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -18868,7 +18868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -19853,7 +19853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -20444,7 +20444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -20641,7 +20641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -21035,7 +21035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -21429,7 +21429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -21823,7 +21823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -22020,7 +22020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -22217,7 +22217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -22414,7 +22414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -22611,7 +22611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -23005,7 +23005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -23202,7 +23202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -23596,7 +23596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -23793,7 +23793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -23990,7 +23990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -24187,7 +24187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -24384,7 +24384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -24778,7 +24778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -24975,7 +24975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -25172,7 +25172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -25369,7 +25369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -25566,7 +25566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -25960,7 +25960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -26157,7 +26157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -26354,7 +26354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -26551,7 +26551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -26748,7 +26748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -26945,7 +26945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -27536,7 +27536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -27733,7 +27733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -27930,7 +27930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -28127,7 +28127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -28324,7 +28324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -28521,7 +28521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -28718,7 +28718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -28915,7 +28915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -29112,7 +29112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -29506,7 +29506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -29703,7 +29703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -29900,7 +29900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -30097,7 +30097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -30294,7 +30294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -30491,7 +30491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -30688,7 +30688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -30885,7 +30885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -31082,7 +31082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -31279,7 +31279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -31476,7 +31476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -31673,7 +31673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -31870,7 +31870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -32067,7 +32067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -32264,7 +32264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -32461,7 +32461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -32658,7 +32658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -32855,7 +32855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -33052,7 +33052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -33249,7 +33249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -33446,7 +33446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -33643,7 +33643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -33840,7 +33840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -34037,7 +34037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -34234,7 +34234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -34431,7 +34431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -34628,7 +34628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -34825,7 +34825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -35022,7 +35022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -35219,7 +35219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -35416,7 +35416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -35613,7 +35613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -35810,7 +35810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -36007,7 +36007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -36204,7 +36204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -36401,7 +36401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -36598,7 +36598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -36795,7 +36795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -36992,7 +36992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -37189,7 +37189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -37386,7 +37386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -37583,7 +37583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -37977,7 +37977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -38174,7 +38174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -38371,7 +38371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -38568,7 +38568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -38765,7 +38765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -38962,7 +38962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -39159,7 +39159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -39356,7 +39356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -39553,7 +39553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -39750,7 +39750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -39947,7 +39947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -40144,7 +40144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -40341,7 +40341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -40538,7 +40538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -40735,7 +40735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -40932,7 +40932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -41129,7 +41129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -41326,7 +41326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -41523,7 +41523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -41720,7 +41720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -41917,7 +41917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -42114,7 +42114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -42311,7 +42311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -42508,7 +42508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -42705,7 +42705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -42902,7 +42902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -43099,7 +43099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -43296,7 +43296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -43493,7 +43493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -43690,7 +43690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -43887,7 +43887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -44084,7 +44084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -44281,7 +44281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -44478,7 +44478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -44675,7 +44675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -44872,7 +44872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -45069,7 +45069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -45266,7 +45266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -45463,7 +45463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -45660,7 +45660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -45857,7 +45857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -46054,7 +46054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -46251,7 +46251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -46448,7 +46448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -46645,7 +46645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -46842,7 +46842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -47039,7 +47039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -47236,7 +47236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -47433,7 +47433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -47630,7 +47630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -47827,7 +47827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -48024,7 +48024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -48221,7 +48221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -48418,7 +48418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -48615,7 +48615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -48812,7 +48812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -49009,7 +49009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -49206,7 +49206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -49403,7 +49403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -49600,7 +49600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -49797,7 +49797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -49994,7 +49994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -50191,7 +50191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -50388,7 +50388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -50585,7 +50585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -50782,7 +50782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -50979,7 +50979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -51176,7 +51176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -51373,7 +51373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -51570,7 +51570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="22">
         <v>237</v>
       </c>
@@ -51767,7 +51767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="22">
         <v>238</v>
       </c>
@@ -51964,7 +51964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="22">
         <v>239</v>
       </c>
@@ -52161,7 +52161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="22">
         <v>240</v>
       </c>
@@ -52358,7 +52358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="22">
         <v>241</v>
       </c>
@@ -52555,7 +52555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="22">
         <v>242</v>
       </c>
@@ -52752,7 +52752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="22">
         <v>243</v>
       </c>
@@ -52949,7 +52949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="22">
         <v>244</v>
       </c>
@@ -53146,7 +53146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="22">
         <v>245</v>
       </c>
@@ -53343,7 +53343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="22">
         <v>246</v>
       </c>
@@ -53540,7 +53540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="22">
         <v>247</v>
       </c>
@@ -53737,7 +53737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="22">
         <v>248</v>
       </c>
@@ -53934,7 +53934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="22">
         <v>249</v>
       </c>
@@ -54131,7 +54131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="22">
         <v>250</v>
       </c>
@@ -54328,7 +54328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="22">
         <v>251</v>
       </c>
@@ -54525,7 +54525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="22">
         <v>252</v>
       </c>
@@ -54722,7 +54722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="22">
         <v>253</v>
       </c>
@@ -54919,7 +54919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="22">
         <v>254</v>
       </c>
@@ -55116,7 +55116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="22">
         <v>255</v>
       </c>
@@ -55313,7 +55313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="22">
         <v>256</v>
       </c>
@@ -55510,7 +55510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="22">
         <v>257</v>
       </c>
@@ -55707,7 +55707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="22">
         <v>258</v>
       </c>
@@ -55904,7 +55904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="22">
         <v>259</v>
       </c>
@@ -56101,7 +56101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="22">
         <v>260</v>
       </c>
@@ -56298,7 +56298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="22">
         <v>261</v>
       </c>
@@ -56495,7 +56495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="22">
         <v>262</v>
       </c>
@@ -56692,7 +56692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="22">
         <v>263</v>
       </c>
@@ -56889,7 +56889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="22">
         <v>264</v>
       </c>
@@ -57086,7 +57086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="22">
         <v>265</v>
       </c>
@@ -57283,7 +57283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="22">
         <v>266</v>
       </c>
@@ -57480,7 +57480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="22">
         <v>267</v>
       </c>
@@ -57677,7 +57677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="22">
         <v>268</v>
       </c>
@@ -57874,7 +57874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="22">
         <v>269</v>
       </c>
@@ -58071,7 +58071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="22">
         <v>270</v>
       </c>
@@ -58268,7 +58268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="22">
         <v>271</v>
       </c>
@@ -58465,7 +58465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="22">
         <v>272</v>
       </c>
@@ -58662,7 +58662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="22">
         <v>273</v>
       </c>
@@ -58859,7 +58859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="22">
         <v>274</v>
       </c>
@@ -59056,7 +59056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="22">
         <v>275</v>
       </c>
@@ -59253,7 +59253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="22">
         <v>276</v>
       </c>
@@ -59450,7 +59450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="22">
         <v>277</v>
       </c>
@@ -59647,7 +59647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="22">
         <v>278</v>
       </c>
@@ -59844,7 +59844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="22">
         <v>279</v>
       </c>
@@ -60041,7 +60041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="22">
         <v>280</v>
       </c>
@@ -60238,7 +60238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="22">
         <v>281</v>
       </c>
@@ -60435,7 +60435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="22">
         <v>282</v>
       </c>
@@ -60632,7 +60632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="22">
         <v>283</v>
       </c>
@@ -60829,7 +60829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="22">
         <v>284</v>
       </c>
@@ -61026,7 +61026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="22">
         <v>285</v>
       </c>
@@ -61223,7 +61223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="22">
         <v>286</v>
       </c>
@@ -61420,7 +61420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="22">
         <v>287</v>
       </c>
@@ -61617,7 +61617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="22">
         <v>288</v>
       </c>
@@ -61814,7 +61814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="22">
         <v>289</v>
       </c>
@@ -62011,7 +62011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="22">
         <v>290</v>
       </c>
@@ -62208,7 +62208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="22">
         <v>291</v>
       </c>
@@ -62405,7 +62405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="22">
         <v>292</v>
       </c>
@@ -62602,7 +62602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="22">
         <v>293</v>
       </c>
@@ -62799,7 +62799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="22">
         <v>294</v>
       </c>
@@ -62996,7 +62996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="22">
         <v>295</v>
       </c>
@@ -63193,7 +63193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="22">
         <v>296</v>
       </c>
@@ -63390,7 +63390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="22">
         <v>297</v>
       </c>
@@ -63587,7 +63587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="22">
         <v>298</v>
       </c>
@@ -63784,7 +63784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="22">
         <v>299</v>
       </c>
@@ -63981,7 +63981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="22">
         <v>300</v>
       </c>
@@ -64178,7 +64178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="22">
         <v>301</v>
       </c>
@@ -64375,7 +64375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="22">
         <v>302</v>
       </c>
@@ -64572,7 +64572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="22">
         <v>303</v>
       </c>
@@ -64769,7 +64769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="22">
         <v>304</v>
       </c>
@@ -64966,7 +64966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="22">
         <v>305</v>
       </c>
@@ -65163,7 +65163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="22">
         <v>306</v>
       </c>
@@ -65360,7 +65360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="22">
         <v>307</v>
       </c>
@@ -65557,7 +65557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="22">
         <v>308</v>
       </c>
@@ -65754,7 +65754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="22">
         <v>309</v>
       </c>
@@ -65951,7 +65951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="22">
         <v>310</v>
       </c>
@@ -66148,7 +66148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="22">
         <v>311</v>
       </c>
@@ -66345,7 +66345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="22">
         <v>312</v>
       </c>
@@ -66542,7 +66542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="22">
         <v>313</v>
       </c>
@@ -66739,7 +66739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="22">
         <v>314</v>
       </c>
@@ -66936,7 +66936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="22">
         <v>315</v>
       </c>
@@ -67133,7 +67133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="22">
         <v>316</v>
       </c>
@@ -67330,7 +67330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A317" s="22">
         <v>317</v>
       </c>
@@ -67527,7 +67527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A318" s="22">
         <v>318</v>
       </c>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A319" s="22">
         <v>319</v>
       </c>
@@ -67921,7 +67921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A320" s="22">
         <v>320</v>
       </c>
@@ -68118,7 +68118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A321" s="22">
         <v>321</v>
       </c>
@@ -68315,7 +68315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A322" s="22">
         <v>322</v>
       </c>
@@ -68512,7 +68512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A323" s="22">
         <v>323</v>
       </c>
@@ -68709,7 +68709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A324" s="22">
         <v>324</v>
       </c>
@@ -68906,7 +68906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A325" s="22">
         <v>325</v>
       </c>
@@ -69103,7 +69103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A326" s="22">
         <v>326</v>
       </c>
@@ -69300,7 +69300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A327" s="22">
         <v>327</v>
       </c>
@@ -69497,7 +69497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A328" s="22">
         <v>328</v>
       </c>
@@ -69694,7 +69694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A329" s="22">
         <v>329</v>
       </c>
@@ -69891,7 +69891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A330" s="22">
         <v>330</v>
       </c>
@@ -70088,7 +70088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A331" s="22">
         <v>331</v>
       </c>
@@ -70285,7 +70285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A332" s="70">
         <v>332</v>
       </c>
@@ -70490,17 +70490,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DE6E4-C53E-4139-972D-243A730EFE26}">
   <dimension ref="A1:E67"/>
-  <sheetFormatPr defaultColWidth="22.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="22.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="49" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" style="49" customWidth="1"/>
+    <col min="3" max="3" width="25.53515625" style="49" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="68" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="22.28515625" style="49"/>
+    <col min="5" max="5" width="32.15234375" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="22.3046875" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="63"/>
       <c r="B1" s="63" t="s">
         <v>936</v>
@@ -70515,7 +70515,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="63"/>
       <c r="B2" s="63" t="s">
         <v>936</v>
@@ -70530,7 +70530,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="s">
         <v>881</v>
       </c>
@@ -70547,7 +70547,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="62" t="s">
         <v>883</v>
       </c>
@@ -70564,7 +70564,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="62" t="s">
         <v>883</v>
       </c>
@@ -70581,7 +70581,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="61" t="s">
         <v>881</v>
       </c>
@@ -70598,7 +70598,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="63"/>
       <c r="B7" s="63" t="s">
         <v>893</v>
@@ -70613,7 +70613,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="62" t="s">
         <v>883</v>
       </c>
@@ -70630,7 +70630,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="63"/>
       <c r="B9" s="63" t="s">
         <v>988</v>
@@ -70645,7 +70645,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="62" t="s">
         <v>884</v>
       </c>
@@ -70662,7 +70662,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="63"/>
       <c r="B11" s="63" t="s">
         <v>936</v>
@@ -70677,7 +70677,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="62" t="s">
         <v>885</v>
       </c>
@@ -70694,7 +70694,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="62" t="s">
         <v>885</v>
       </c>
@@ -70711,7 +70711,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="63"/>
       <c r="B14" s="63" t="s">
         <v>893</v>
@@ -70726,7 +70726,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="62" t="s">
         <v>886</v>
       </c>
@@ -70743,7 +70743,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="62" t="s">
         <v>886</v>
       </c>
@@ -70760,7 +70760,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="63"/>
       <c r="B17" s="63" t="s">
         <v>936</v>
@@ -70775,7 +70775,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="63"/>
       <c r="B18" s="63" t="s">
         <v>893</v>
@@ -70790,7 +70790,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
         <v>881</v>
       </c>
@@ -70807,7 +70807,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="63"/>
       <c r="B20" s="63" t="s">
         <v>912</v>
@@ -70822,7 +70822,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="62" t="s">
         <v>884</v>
       </c>
@@ -70839,7 +70839,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="62" t="s">
         <v>884</v>
       </c>
@@ -70856,7 +70856,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="62" t="s">
         <v>885</v>
       </c>
@@ -70873,7 +70873,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="61" t="s">
         <v>882</v>
       </c>
@@ -70890,7 +70890,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="63"/>
       <c r="B25" s="63" t="s">
         <v>893</v>
@@ -70905,7 +70905,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="61" t="s">
         <v>881</v>
       </c>
@@ -70922,7 +70922,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="62" t="s">
         <v>884</v>
       </c>
@@ -70939,7 +70939,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="63"/>
       <c r="B28" s="63" t="s">
         <v>936</v>
@@ -70954,7 +70954,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
         <v>884</v>
       </c>
@@ -70971,7 +70971,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="61" t="s">
         <v>881</v>
       </c>
@@ -70988,7 +70988,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="62" t="s">
         <v>886</v>
       </c>
@@ -71005,7 +71005,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="61" t="s">
         <v>882</v>
       </c>
@@ -71022,7 +71022,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="61" t="s">
         <v>882</v>
       </c>
@@ -71039,7 +71039,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="61" t="s">
         <v>882</v>
       </c>
@@ -71056,7 +71056,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="61" t="s">
         <v>882</v>
       </c>
@@ -71073,7 +71073,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="61" t="s">
         <v>882</v>
       </c>
@@ -71090,7 +71090,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="63"/>
       <c r="B37" s="63" t="s">
         <v>893</v>
@@ -71105,7 +71105,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="61" t="s">
         <v>882</v>
       </c>
@@ -71122,7 +71122,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="63"/>
       <c r="B39" s="63" t="s">
         <v>893</v>
@@ -71137,7 +71137,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="62" t="s">
         <v>883</v>
       </c>
@@ -71154,7 +71154,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="62" t="s">
         <v>886</v>
       </c>
@@ -71171,7 +71171,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="63"/>
       <c r="B42" s="63" t="s">
         <v>893</v>
@@ -71186,7 +71186,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="62" t="s">
         <v>886</v>
       </c>
@@ -71203,7 +71203,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="61" t="s">
         <v>881</v>
       </c>
@@ -71220,7 +71220,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="63"/>
       <c r="B45" s="63" t="s">
         <v>912</v>
@@ -71235,7 +71235,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="61" t="s">
         <v>881</v>
       </c>
@@ -71252,7 +71252,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="63"/>
       <c r="B47" s="63" t="s">
         <v>893</v>
@@ -71267,7 +71267,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="63"/>
       <c r="B48" s="63" t="s">
         <v>893</v>
@@ -71282,7 +71282,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="63"/>
       <c r="B49" s="63" t="s">
         <v>893</v>
@@ -71297,7 +71297,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="63"/>
       <c r="B50" s="63" t="s">
         <v>936</v>
@@ -71312,7 +71312,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="63"/>
       <c r="B51" s="63" t="s">
         <v>893</v>
@@ -71327,7 +71327,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="62" t="s">
         <v>885</v>
       </c>
@@ -71344,7 +71344,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="62" t="s">
         <v>885</v>
       </c>
@@ -71361,7 +71361,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="62" t="s">
         <v>886</v>
       </c>
@@ -71378,7 +71378,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="62" t="s">
         <v>885</v>
       </c>
@@ -71395,7 +71395,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="63"/>
       <c r="B56" s="63" t="s">
         <v>893</v>
@@ -71410,7 +71410,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="63"/>
       <c r="B57" s="63" t="s">
         <v>893</v>
@@ -71425,7 +71425,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="61" t="s">
         <v>881</v>
       </c>
@@ -71442,7 +71442,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="62" t="s">
         <v>884</v>
       </c>
@@ -71459,7 +71459,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="63"/>
       <c r="B60" s="63" t="s">
         <v>893</v>
@@ -71474,7 +71474,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="63"/>
       <c r="B61" s="63" t="s">
         <v>912</v>
@@ -71489,7 +71489,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="63"/>
       <c r="B62" s="63" t="s">
         <v>912</v>
@@ -71504,7 +71504,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="63"/>
       <c r="B63" s="63" t="s">
         <v>912</v>
@@ -71519,7 +71519,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="63"/>
       <c r="B64" s="63" t="s">
         <v>912</v>
@@ -71534,7 +71534,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="63"/>
       <c r="B65" s="63" t="s">
         <v>936</v>
@@ -71549,7 +71549,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="61" t="s">
         <v>882</v>
       </c>
@@ -71566,7 +71566,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="61" t="s">
         <v>882</v>
       </c>
@@ -71599,15 +71599,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2354D58-A693-4C70-9179-E7934BAB386F}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="53.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="53.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="49" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="49" customWidth="1"/>
-    <col min="4" max="16384" width="53.140625" style="49"/>
+    <col min="1" max="1" width="10.15234375" style="49" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" style="49" customWidth="1"/>
+    <col min="3" max="3" width="21.3828125" style="49" customWidth="1"/>
+    <col min="4" max="16384" width="53.15234375" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
         <v>872</v>
       </c>
@@ -71618,7 +71618,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="61" t="s">
         <v>860</v>
       </c>
@@ -71629,7 +71629,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="s">
         <v>863</v>
       </c>
@@ -71640,7 +71640,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="61" t="s">
         <v>857</v>
       </c>
@@ -71651,7 +71651,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
         <v>875</v>
       </c>
@@ -71662,7 +71662,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="61" t="s">
         <v>866</v>
       </c>
@@ -71673,7 +71673,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="61" t="s">
         <v>869</v>
       </c>
@@ -71684,7 +71684,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="61" t="s">
         <v>878</v>
       </c>

--- a/Versão5/SUS/Ontologia_RDC_50.xlsx
+++ b/Versão5/SUS/Ontologia_RDC_50.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4752F0-CCDF-4633-B224-DFE708924768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C49360-F87C-4D45-AF90-F78876D8983C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -3495,7 +3495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3713,7 +3713,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3735,13 +3734,33 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
     <dxf>
@@ -3749,23 +3768,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -3806,22 +3809,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3843,44 +3830,8 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4208,15 +4159,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="93.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="93.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>45</v>
       </c>
@@ -4227,7 +4178,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>47</v>
       </c>
@@ -4238,7 +4189,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>48</v>
       </c>
@@ -4249,7 +4200,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>49</v>
       </c>
@@ -4260,7 +4211,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>50</v>
       </c>
@@ -4272,7 +4223,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>51</v>
       </c>
@@ -4284,7 +4235,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>52</v>
       </c>
@@ -4295,7 +4246,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>54</v>
       </c>
@@ -4306,7 +4257,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>55</v>
       </c>
@@ -4317,7 +4268,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>57</v>
       </c>
@@ -4328,7 +4279,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>59</v>
       </c>
@@ -4339,7 +4290,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>60</v>
       </c>
@@ -4350,7 +4301,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>61</v>
       </c>
@@ -4361,7 +4312,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>62</v>
       </c>
@@ -4372,7 +4323,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>63</v>
       </c>
@@ -4383,7 +4334,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>64</v>
       </c>
@@ -4394,7 +4345,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>65</v>
       </c>
@@ -4405,19 +4356,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46258.574957291668</v>
+        <v>46264.578267476849</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>67</v>
       </c>
@@ -4428,7 +4379,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>68</v>
       </c>
@@ -4439,7 +4390,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>88</v>
       </c>
@@ -4450,7 +4401,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
         <v>87</v>
       </c>
@@ -4462,7 +4413,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>89</v>
       </c>
@@ -4474,7 +4425,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>69</v>
       </c>
@@ -4485,7 +4436,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>70</v>
       </c>
@@ -4497,7 +4448,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="17" t="s">
         <v>82</v>
       </c>
@@ -4509,7 +4460,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="15" t="s">
         <v>90</v>
       </c>
@@ -4520,7 +4471,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="15" t="s">
         <v>92</v>
       </c>
@@ -4531,7 +4482,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
         <v>94</v>
       </c>
@@ -4542,7 +4493,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>96</v>
       </c>
@@ -4553,7 +4504,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>98</v>
       </c>
@@ -4564,7 +4515,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>100</v>
       </c>
@@ -4575,7 +4526,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>102</v>
       </c>
@@ -4586,7 +4537,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>104</v>
       </c>
@@ -4597,7 +4548,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>106</v>
       </c>
@@ -4608,7 +4559,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>108</v>
       </c>
@@ -4619,7 +4570,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>110</v>
       </c>
@@ -4630,7 +4581,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="17" t="s">
         <v>112</v>
       </c>
@@ -4641,7 +4592,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="46" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="46" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>114</v>
       </c>
@@ -4652,7 +4603,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>116</v>
       </c>
@@ -4663,7 +4614,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="56" t="s">
         <v>768</v>
       </c>
@@ -4692,36 +4643,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultColWidth="5.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" style="1"/>
-    <col min="4" max="4" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="79" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.84375" style="1"/>
+    <col min="4" max="4" width="5.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3046875" style="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.15234375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3046875" style="8" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="5.85546875" style="1"/>
+    <col min="29" max="29" width="5.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="5.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>44</v>
       </c>
@@ -4810,7 +4761,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37">
         <v>2</v>
       </c>
@@ -4906,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37">
         <v>3</v>
       </c>
@@ -5002,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37">
         <v>4</v>
       </c>
@@ -5013,10 +4964,10 @@
         <v>1001</v>
       </c>
       <c r="D4" s="73" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E4" s="73" t="s">
         <v>1002</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>1003</v>
       </c>
       <c r="F4" s="73" t="s">
         <v>1004</v>
@@ -5042,11 +4993,11 @@
       </c>
       <c r="M4" s="38" t="str">
         <f t="shared" si="9"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N4" s="38" t="str">
         <f t="shared" si="9"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O4" s="38" t="str">
         <f t="shared" si="9"/>
@@ -5070,11 +5021,11 @@
       </c>
       <c r="U4" s="39" t="str">
         <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V4" s="74" t="str">
         <f t="shared" si="10"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W4" s="39" t="s">
         <v>995</v>
@@ -5104,35 +5055,35 @@
     <sortCondition ref="A1:A2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:AC1 AD1:XFD3 T2:W3 A5:XFD1048576 A2:A4 W4">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+  <conditionalFormatting sqref="A1:AC1 AD1:XFD3 T2:W3 A2:A4 W4 A5:XFD1048576">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="16" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="15" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:R3">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R4">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5148,19 +5099,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -5225,7 +5176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -5293,7 +5244,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5309,14 +5260,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -5327,7 +5278,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -5340,7 +5291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5351,76 +5302,76 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5247C9F-0832-49D6-8CCC-8F4A7A71BCAA}">
   <dimension ref="A1:BM337"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.69140625" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.84375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.69140625" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="7" max="7" width="5.69140625" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.69140625" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.69140625" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.69140625" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="5.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.69140625" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="5.69140625" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" customWidth="1"/>
+    <col min="19" max="19" width="5.69140625" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="5.69140625" customWidth="1"/>
     <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="23" width="5.7109375" customWidth="1"/>
+    <col min="23" max="23" width="5.69140625" customWidth="1"/>
     <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="25" width="5.7109375" customWidth="1"/>
+    <col min="25" max="25" width="5.69140625" customWidth="1"/>
     <col min="26" max="26" width="8" customWidth="1"/>
-    <col min="27" max="27" width="5.7109375" customWidth="1"/>
+    <col min="27" max="27" width="5.69140625" customWidth="1"/>
     <col min="28" max="28" width="8" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" customWidth="1"/>
+    <col min="29" max="29" width="5.69140625" customWidth="1"/>
     <col min="30" max="30" width="8" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
+    <col min="31" max="31" width="5.69140625" customWidth="1"/>
     <col min="32" max="32" width="8" customWidth="1"/>
-    <col min="33" max="33" width="5.7109375" customWidth="1"/>
+    <col min="33" max="33" width="5.69140625" customWidth="1"/>
     <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="35" width="5.7109375" customWidth="1"/>
+    <col min="35" max="35" width="5.69140625" customWidth="1"/>
     <col min="36" max="36" width="8" customWidth="1"/>
-    <col min="37" max="37" width="5.7109375" customWidth="1"/>
+    <col min="37" max="37" width="5.69140625" customWidth="1"/>
     <col min="38" max="38" width="8" customWidth="1"/>
-    <col min="39" max="39" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="5.69140625" customWidth="1"/>
     <col min="40" max="40" width="8" customWidth="1"/>
-    <col min="41" max="41" width="5.7109375" customWidth="1"/>
+    <col min="41" max="41" width="5.69140625" customWidth="1"/>
     <col min="42" max="42" width="8" customWidth="1"/>
-    <col min="43" max="43" width="5.7109375" customWidth="1"/>
+    <col min="43" max="43" width="5.69140625" customWidth="1"/>
     <col min="44" max="44" width="8" customWidth="1"/>
-    <col min="45" max="45" width="5.7109375" customWidth="1"/>
+    <col min="45" max="45" width="5.69140625" customWidth="1"/>
     <col min="46" max="46" width="8" customWidth="1"/>
-    <col min="47" max="47" width="5.7109375" customWidth="1"/>
+    <col min="47" max="47" width="5.69140625" customWidth="1"/>
     <col min="48" max="48" width="8" customWidth="1"/>
-    <col min="49" max="49" width="5.7109375" customWidth="1"/>
-    <col min="50" max="50" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="5.69140625" customWidth="1"/>
+    <col min="50" max="50" width="4.3046875" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="6" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.5703125" customWidth="1"/>
+    <col min="52" max="52" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.53515625" customWidth="1"/>
     <col min="54" max="54" width="6" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="103.140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="103.15234375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="2.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -5617,7 +5568,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -5814,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -6011,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -6208,7 +6159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -6405,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -6602,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -6799,7 +6750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -6996,7 +6947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -7193,7 +7144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -7390,7 +7341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -7587,7 +7538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7784,7 +7735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7981,7 +7932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -8178,7 +8129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -8375,7 +8326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -8572,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -8769,7 +8720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -8966,7 +8917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -9163,7 +9114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -9360,7 +9311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -9557,7 +9508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -9754,7 +9705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -9951,7 +9902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -10148,7 +10099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -10345,7 +10296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -10542,7 +10493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -10739,7 +10690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -10936,7 +10887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -11133,7 +11084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -11330,7 +11281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -11527,7 +11478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -11724,7 +11675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -11921,7 +11872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -12118,7 +12069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -12315,7 +12266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -12512,7 +12463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -12709,7 +12660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -12906,7 +12857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -13103,7 +13054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -13300,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -13497,7 +13448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -13694,7 +13645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -13891,7 +13842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -14088,7 +14039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -14285,7 +14236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -14482,7 +14433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -14679,7 +14630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -14876,7 +14827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -15073,7 +15024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -15270,7 +15221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -15467,7 +15418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -15664,7 +15615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -15861,7 +15812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -16058,7 +16009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -16255,7 +16206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -16452,7 +16403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -16649,7 +16600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -16846,7 +16797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -17043,7 +16994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -17240,7 +17191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -17437,7 +17388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -17634,7 +17585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -17831,7 +17782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -18028,7 +17979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -18225,7 +18176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -18422,7 +18373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -18619,7 +18570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -18816,7 +18767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -19013,7 +18964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -19210,7 +19161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -19407,7 +19358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -19604,7 +19555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -19801,7 +19752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -19998,7 +19949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -20195,7 +20146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -20392,7 +20343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -20589,7 +20540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -20786,7 +20737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -20983,7 +20934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -21180,7 +21131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -21377,7 +21328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -21574,7 +21525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -21771,7 +21722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -21968,7 +21919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -22165,7 +22116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -22362,7 +22313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -22559,7 +22510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -22756,7 +22707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -22953,7 +22904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -23150,7 +23101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -23347,7 +23298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -23544,7 +23495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -23741,7 +23692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -23938,7 +23889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -24135,7 +24086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -24332,7 +24283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -24529,7 +24480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -24726,7 +24677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -24923,7 +24874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -25120,7 +25071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -25317,7 +25268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -25514,7 +25465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -25711,7 +25662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -25908,7 +25859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -26105,7 +26056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -26302,7 +26253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -26499,7 +26450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -26696,7 +26647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -26893,7 +26844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -27090,7 +27041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -27287,7 +27238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -27484,7 +27435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -27681,7 +27632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -27878,7 +27829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -28075,7 +28026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -28272,7 +28223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -28469,7 +28420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -28666,7 +28617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -28863,7 +28814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -29060,7 +29011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -29257,7 +29208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -29454,7 +29405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -29651,7 +29602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -29848,7 +29799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -30045,7 +29996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -30242,7 +30193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -30439,7 +30390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -30636,7 +30587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -30833,7 +30784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -31030,7 +30981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -31227,7 +31178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -31424,7 +31375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -31621,7 +31572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -31818,7 +31769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -32015,7 +31966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -32212,7 +32163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -32409,7 +32360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -32606,7 +32557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -32803,7 +32754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -33000,7 +32951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -33197,7 +33148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -33394,7 +33345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -33591,7 +33542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -33788,7 +33739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -33985,7 +33936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -34182,7 +34133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -34379,7 +34330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -34576,7 +34527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -34773,7 +34724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -34970,7 +34921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -35167,7 +35118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -35364,7 +35315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -35561,7 +35512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -35758,7 +35709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -35955,7 +35906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -36152,7 +36103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -36349,7 +36300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -36546,7 +36497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -36743,7 +36694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -36940,7 +36891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -37137,7 +37088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -37334,7 +37285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -37531,7 +37482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -37728,7 +37679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -37925,7 +37876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -38122,7 +38073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -38319,7 +38270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -38516,7 +38467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -38713,7 +38664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -38910,7 +38861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -39107,7 +39058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -39304,7 +39255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -39501,7 +39452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -39698,7 +39649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -39895,7 +39846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -40092,7 +40043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -40289,7 +40240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -40486,7 +40437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -40683,7 +40634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -40880,7 +40831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -41077,7 +41028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -41274,7 +41225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -41471,7 +41422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -41668,7 +41619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -41865,7 +41816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -42062,7 +42013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -42259,7 +42210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -42456,7 +42407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -42653,7 +42604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -42850,7 +42801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -43047,7 +42998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -43244,7 +43195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -43441,7 +43392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -43638,7 +43589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -43835,7 +43786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -44032,7 +43983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -44229,7 +44180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -44426,7 +44377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -44623,7 +44574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -44820,7 +44771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -45017,7 +44968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -45214,7 +45165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -45411,7 +45362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -45608,7 +45559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -45805,7 +45756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -46002,7 +45953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -46199,7 +46150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -46396,7 +46347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -46593,7 +46544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -46790,7 +46741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -46987,7 +46938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -47184,7 +47135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -47381,7 +47332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -47578,7 +47529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -47775,7 +47726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -47972,7 +47923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -48169,7 +48120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -48366,7 +48317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -48563,7 +48514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -48760,7 +48711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -48957,7 +48908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -49154,7 +49105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -49351,7 +49302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -49548,7 +49499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -49745,7 +49696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -49942,7 +49893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -50139,7 +50090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -50336,7 +50287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -50533,7 +50484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -50730,7 +50681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -50927,7 +50878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -51124,7 +51075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -51321,7 +51272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -51518,7 +51469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -51715,7 +51666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -51912,7 +51863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="22">
         <v>237</v>
       </c>
@@ -52109,7 +52060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="22">
         <v>238</v>
       </c>
@@ -52306,7 +52257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="22">
         <v>239</v>
       </c>
@@ -52503,7 +52454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="22">
         <v>240</v>
       </c>
@@ -52700,7 +52651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="22">
         <v>241</v>
       </c>
@@ -52897,7 +52848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="22">
         <v>242</v>
       </c>
@@ -53094,7 +53045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="22">
         <v>243</v>
       </c>
@@ -53291,7 +53242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="22">
         <v>244</v>
       </c>
@@ -53488,7 +53439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="22">
         <v>245</v>
       </c>
@@ -53685,7 +53636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="22">
         <v>246</v>
       </c>
@@ -53882,7 +53833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="22">
         <v>247</v>
       </c>
@@ -54079,7 +54030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="22">
         <v>248</v>
       </c>
@@ -54276,7 +54227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="22">
         <v>249</v>
       </c>
@@ -54473,7 +54424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="22">
         <v>250</v>
       </c>
@@ -54670,7 +54621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="22">
         <v>251</v>
       </c>
@@ -54867,7 +54818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="22">
         <v>252</v>
       </c>
@@ -55064,7 +55015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="22">
         <v>253</v>
       </c>
@@ -55261,7 +55212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="22">
         <v>254</v>
       </c>
@@ -55458,7 +55409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="22">
         <v>255</v>
       </c>
@@ -55655,7 +55606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="22">
         <v>256</v>
       </c>
@@ -55852,7 +55803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="22">
         <v>257</v>
       </c>
@@ -56049,7 +56000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="22">
         <v>258</v>
       </c>
@@ -56246,7 +56197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="22">
         <v>259</v>
       </c>
@@ -56443,7 +56394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="22">
         <v>260</v>
       </c>
@@ -56640,7 +56591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="22">
         <v>261</v>
       </c>
@@ -56837,7 +56788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="22">
         <v>262</v>
       </c>
@@ -57034,7 +56985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="22">
         <v>263</v>
       </c>
@@ -57231,7 +57182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="22">
         <v>264</v>
       </c>
@@ -57428,7 +57379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="22">
         <v>265</v>
       </c>
@@ -57625,7 +57576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="22">
         <v>266</v>
       </c>
@@ -57822,7 +57773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="22">
         <v>267</v>
       </c>
@@ -58019,7 +57970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="22">
         <v>268</v>
       </c>
@@ -58216,7 +58167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="22">
         <v>269</v>
       </c>
@@ -58413,7 +58364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="22">
         <v>270</v>
       </c>
@@ -58610,7 +58561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="22">
         <v>271</v>
       </c>
@@ -58807,7 +58758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="22">
         <v>272</v>
       </c>
@@ -59004,7 +58955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="22">
         <v>273</v>
       </c>
@@ -59201,7 +59152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="22">
         <v>274</v>
       </c>
@@ -59398,7 +59349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="22">
         <v>275</v>
       </c>
@@ -59595,7 +59546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="22">
         <v>276</v>
       </c>
@@ -59792,7 +59743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="22">
         <v>277</v>
       </c>
@@ -59989,7 +59940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="22">
         <v>278</v>
       </c>
@@ -60186,7 +60137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="22">
         <v>279</v>
       </c>
@@ -60383,7 +60334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="22">
         <v>280</v>
       </c>
@@ -60580,7 +60531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="22">
         <v>281</v>
       </c>
@@ -60777,7 +60728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="22">
         <v>282</v>
       </c>
@@ -60974,7 +60925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="22">
         <v>283</v>
       </c>
@@ -61171,7 +61122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="22">
         <v>284</v>
       </c>
@@ -61368,7 +61319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="22">
         <v>285</v>
       </c>
@@ -61565,7 +61516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="22">
         <v>286</v>
       </c>
@@ -61762,7 +61713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="22">
         <v>287</v>
       </c>
@@ -61959,7 +61910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="22">
         <v>288</v>
       </c>
@@ -62156,7 +62107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="22">
         <v>289</v>
       </c>
@@ -62353,7 +62304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="22">
         <v>290</v>
       </c>
@@ -62550,7 +62501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="22">
         <v>291</v>
       </c>
@@ -62747,7 +62698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="22">
         <v>292</v>
       </c>
@@ -62944,7 +62895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="22">
         <v>293</v>
       </c>
@@ -63141,7 +63092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="22">
         <v>294</v>
       </c>
@@ -63338,7 +63289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="22">
         <v>295</v>
       </c>
@@ -63535,7 +63486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="22">
         <v>296</v>
       </c>
@@ -63732,7 +63683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="22">
         <v>297</v>
       </c>
@@ -63929,7 +63880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="22">
         <v>298</v>
       </c>
@@ -64126,7 +64077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="22">
         <v>299</v>
       </c>
@@ -64323,7 +64274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="22">
         <v>300</v>
       </c>
@@ -64520,7 +64471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="22">
         <v>301</v>
       </c>
@@ -64717,7 +64668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="22">
         <v>302</v>
       </c>
@@ -64914,7 +64865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="22">
         <v>303</v>
       </c>
@@ -65111,7 +65062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="22">
         <v>304</v>
       </c>
@@ -65308,7 +65259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="22">
         <v>305</v>
       </c>
@@ -65505,7 +65456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="22">
         <v>306</v>
       </c>
@@ -65702,7 +65653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="22">
         <v>307</v>
       </c>
@@ -65899,7 +65850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="22">
         <v>308</v>
       </c>
@@ -66096,7 +66047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="22">
         <v>309</v>
       </c>
@@ -66293,7 +66244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="22">
         <v>310</v>
       </c>
@@ -66490,7 +66441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="22">
         <v>311</v>
       </c>
@@ -66687,7 +66638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="22">
         <v>312</v>
       </c>
@@ -66884,7 +66835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="22">
         <v>313</v>
       </c>
@@ -67081,7 +67032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="22">
         <v>314</v>
       </c>
@@ -67278,7 +67229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="22">
         <v>315</v>
       </c>
@@ -67475,7 +67426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="22">
         <v>316</v>
       </c>
@@ -67672,7 +67623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A317" s="22">
         <v>317</v>
       </c>
@@ -67869,7 +67820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A318" s="22">
         <v>318</v>
       </c>
@@ -68066,7 +68017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A319" s="22">
         <v>319</v>
       </c>
@@ -68263,7 +68214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A320" s="22">
         <v>320</v>
       </c>
@@ -68460,7 +68411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A321" s="22">
         <v>321</v>
       </c>
@@ -68657,7 +68608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A322" s="22">
         <v>322</v>
       </c>
@@ -68854,7 +68805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A323" s="22">
         <v>323</v>
       </c>
@@ -69051,7 +69002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A324" s="22">
         <v>324</v>
       </c>
@@ -69248,7 +69199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A325" s="22">
         <v>325</v>
       </c>
@@ -69445,7 +69396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A326" s="22">
         <v>326</v>
       </c>
@@ -69642,7 +69593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A327" s="22">
         <v>327</v>
       </c>
@@ -69839,7 +69790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A328" s="22">
         <v>328</v>
       </c>
@@ -70036,7 +69987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A329" s="22">
         <v>329</v>
       </c>
@@ -70233,7 +70184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A330" s="22">
         <v>330</v>
       </c>
@@ -70430,7 +70381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A331" s="22">
         <v>331</v>
       </c>
@@ -70627,7 +70578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:65" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:65" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A332" s="22">
         <v>332</v>
       </c>
@@ -70824,14 +70775,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:65" s="83" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:65" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="22">
         <v>333</v>
       </c>
-      <c r="B333" s="84" t="s">
+      <c r="B333" s="83" t="s">
         <v>1008</v>
       </c>
-      <c r="C333" s="85" t="s">
+      <c r="C333" s="84" t="s">
         <v>1004</v>
       </c>
       <c r="D333" s="68" t="s">
@@ -70978,14 +70929,14 @@
       <c r="AY333" s="66" t="s">
         <v>1009</v>
       </c>
-      <c r="AZ333" s="80" t="str">
+      <c r="AZ333" s="79" t="str">
         <f t="shared" ref="AZ333:AZ337" si="0">IF(BA333="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="BA333" s="81" t="s">
+      <c r="BA333" s="80" t="s">
         <v>1010</v>
       </c>
-      <c r="BB333" s="82" t="s">
+      <c r="BB333" s="81" t="s">
         <v>73</v>
       </c>
       <c r="BC333" s="66" t="s">
@@ -71022,14 +70973,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:65" s="83" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:65" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="22">
         <v>334</v>
       </c>
-      <c r="B334" s="84" t="s">
+      <c r="B334" s="83" t="s">
         <v>1012</v>
       </c>
-      <c r="C334" s="85" t="s">
+      <c r="C334" s="84" t="s">
         <v>1004</v>
       </c>
       <c r="D334" s="68" t="s">
@@ -71176,14 +71127,14 @@
       <c r="AY334" s="66" t="s">
         <v>1009</v>
       </c>
-      <c r="AZ334" s="80" t="str">
+      <c r="AZ334" s="79" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="BA334" s="81" t="s">
+      <c r="BA334" s="80" t="s">
         <v>1013</v>
       </c>
-      <c r="BB334" s="82" t="s">
+      <c r="BB334" s="81" t="s">
         <v>73</v>
       </c>
       <c r="BC334" s="66" t="s">
@@ -71220,14 +71171,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:65" s="83" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:65" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="22">
         <v>335</v>
       </c>
-      <c r="B335" s="84" t="s">
+      <c r="B335" s="83" t="s">
         <v>1015</v>
       </c>
-      <c r="C335" s="85" t="s">
+      <c r="C335" s="84" t="s">
         <v>1004</v>
       </c>
       <c r="D335" s="68" t="s">
@@ -71374,14 +71325,14 @@
       <c r="AY335" s="66" t="s">
         <v>1009</v>
       </c>
-      <c r="AZ335" s="80" t="str">
+      <c r="AZ335" s="79" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="BA335" s="81" t="s">
+      <c r="BA335" s="80" t="s">
         <v>1016</v>
       </c>
-      <c r="BB335" s="82" t="s">
+      <c r="BB335" s="81" t="s">
         <v>73</v>
       </c>
       <c r="BC335" s="66" t="s">
@@ -71418,14 +71369,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:65" s="83" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:65" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="22">
         <v>336</v>
       </c>
-      <c r="B336" s="84" t="s">
+      <c r="B336" s="83" t="s">
         <v>1018</v>
       </c>
-      <c r="C336" s="85" t="s">
+      <c r="C336" s="84" t="s">
         <v>1004</v>
       </c>
       <c r="D336" s="68" t="s">
@@ -71572,14 +71523,14 @@
       <c r="AY336" s="66" t="s">
         <v>1009</v>
       </c>
-      <c r="AZ336" s="80" t="str">
+      <c r="AZ336" s="79" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="BA336" s="81" t="s">
+      <c r="BA336" s="80" t="s">
         <v>1019</v>
       </c>
-      <c r="BB336" s="82" t="s">
+      <c r="BB336" s="81" t="s">
         <v>73</v>
       </c>
       <c r="BC336" s="66" t="s">
@@ -71616,14 +71567,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:65" s="83" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:65" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="22">
         <v>337</v>
       </c>
-      <c r="B337" s="84" t="s">
+      <c r="B337" s="83" t="s">
         <v>1021</v>
       </c>
-      <c r="C337" s="85" t="s">
+      <c r="C337" s="84" t="s">
         <v>1004</v>
       </c>
       <c r="D337" s="68" t="s">
@@ -71770,14 +71721,14 @@
       <c r="AY337" s="66" t="s">
         <v>1009</v>
       </c>
-      <c r="AZ337" s="80" t="str">
+      <c r="AZ337" s="79" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="BA337" s="81" t="s">
+      <c r="BA337" s="80" t="s">
         <v>1022</v>
       </c>
-      <c r="BB337" s="82" t="s">
+      <c r="BB337" s="81" t="s">
         <v>73</v>
       </c>
       <c r="BC337" s="66" t="s">
@@ -71816,8 +71767,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B333:B337">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -71826,17 +71777,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DE6E4-C53E-4139-972D-243A730EFE26}">
   <dimension ref="A1:E67"/>
-  <sheetFormatPr defaultColWidth="22.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="22.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="46" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="46" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="25.53515625" style="46" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="65" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="22.28515625" style="46"/>
+    <col min="5" max="5" width="32.15234375" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="22.3046875" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="60"/>
       <c r="B1" s="60" t="s">
         <v>933</v>
@@ -71851,7 +71802,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="60"/>
       <c r="B2" s="60" t="s">
         <v>933</v>
@@ -71866,7 +71817,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="58" t="s">
         <v>878</v>
       </c>
@@ -71883,7 +71834,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="59" t="s">
         <v>880</v>
       </c>
@@ -71900,7 +71851,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="59" t="s">
         <v>880</v>
       </c>
@@ -71917,7 +71868,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="58" t="s">
         <v>878</v>
       </c>
@@ -71934,7 +71885,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="60"/>
       <c r="B7" s="60" t="s">
         <v>890</v>
@@ -71949,7 +71900,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="59" t="s">
         <v>880</v>
       </c>
@@ -71966,7 +71917,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="60"/>
       <c r="B9" s="60" t="s">
         <v>985</v>
@@ -71981,7 +71932,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="59" t="s">
         <v>881</v>
       </c>
@@ -71998,7 +71949,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="60"/>
       <c r="B11" s="60" t="s">
         <v>933</v>
@@ -72013,7 +71964,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="59" t="s">
         <v>882</v>
       </c>
@@ -72030,7 +71981,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="59" t="s">
         <v>882</v>
       </c>
@@ -72047,7 +71998,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="60"/>
       <c r="B14" s="60" t="s">
         <v>890</v>
@@ -72062,7 +72013,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="59" t="s">
         <v>883</v>
       </c>
@@ -72079,7 +72030,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="59" t="s">
         <v>883</v>
       </c>
@@ -72096,7 +72047,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="60"/>
       <c r="B17" s="60" t="s">
         <v>933</v>
@@ -72111,7 +72062,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="60"/>
       <c r="B18" s="60" t="s">
         <v>890</v>
@@ -72126,7 +72077,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="58" t="s">
         <v>878</v>
       </c>
@@ -72143,7 +72094,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="60"/>
       <c r="B20" s="60" t="s">
         <v>909</v>
@@ -72158,7 +72109,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="59" t="s">
         <v>881</v>
       </c>
@@ -72175,7 +72126,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="59" t="s">
         <v>881</v>
       </c>
@@ -72192,7 +72143,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="59" t="s">
         <v>882</v>
       </c>
@@ -72209,7 +72160,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="58" t="s">
         <v>879</v>
       </c>
@@ -72226,7 +72177,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="60"/>
       <c r="B25" s="60" t="s">
         <v>890</v>
@@ -72241,7 +72192,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="58" t="s">
         <v>878</v>
       </c>
@@ -72258,7 +72209,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="59" t="s">
         <v>881</v>
       </c>
@@ -72275,7 +72226,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="60"/>
       <c r="B28" s="60" t="s">
         <v>933</v>
@@ -72290,7 +72241,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="59" t="s">
         <v>881</v>
       </c>
@@ -72307,7 +72258,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="58" t="s">
         <v>878</v>
       </c>
@@ -72324,7 +72275,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="59" t="s">
         <v>883</v>
       </c>
@@ -72341,7 +72292,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="58" t="s">
         <v>879</v>
       </c>
@@ -72358,7 +72309,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="58" t="s">
         <v>879</v>
       </c>
@@ -72375,7 +72326,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="58" t="s">
         <v>879</v>
       </c>
@@ -72392,7 +72343,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="58" t="s">
         <v>879</v>
       </c>
@@ -72409,7 +72360,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="58" t="s">
         <v>879</v>
       </c>
@@ -72426,7 +72377,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="60"/>
       <c r="B37" s="60" t="s">
         <v>890</v>
@@ -72441,7 +72392,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="58" t="s">
         <v>879</v>
       </c>
@@ -72458,7 +72409,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="60"/>
       <c r="B39" s="60" t="s">
         <v>890</v>
@@ -72473,7 +72424,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="59" t="s">
         <v>880</v>
       </c>
@@ -72490,7 +72441,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="59" t="s">
         <v>883</v>
       </c>
@@ -72507,7 +72458,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="60"/>
       <c r="B42" s="60" t="s">
         <v>890</v>
@@ -72522,7 +72473,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="59" t="s">
         <v>883</v>
       </c>
@@ -72539,7 +72490,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="58" t="s">
         <v>878</v>
       </c>
@@ -72556,7 +72507,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="60"/>
       <c r="B45" s="60" t="s">
         <v>909</v>
@@ -72571,7 +72522,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="58" t="s">
         <v>878</v>
       </c>
@@ -72588,7 +72539,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="60"/>
       <c r="B47" s="60" t="s">
         <v>890</v>
@@ -72603,7 +72554,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="60"/>
       <c r="B48" s="60" t="s">
         <v>890</v>
@@ -72618,7 +72569,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="60"/>
       <c r="B49" s="60" t="s">
         <v>890</v>
@@ -72633,7 +72584,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="60"/>
       <c r="B50" s="60" t="s">
         <v>933</v>
@@ -72648,7 +72599,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="60"/>
       <c r="B51" s="60" t="s">
         <v>890</v>
@@ -72663,7 +72614,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="59" t="s">
         <v>882</v>
       </c>
@@ -72680,7 +72631,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="59" t="s">
         <v>882</v>
       </c>
@@ -72697,7 +72648,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="59" t="s">
         <v>883</v>
       </c>
@@ -72714,7 +72665,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="59" t="s">
         <v>882</v>
       </c>
@@ -72731,7 +72682,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="60"/>
       <c r="B56" s="60" t="s">
         <v>890</v>
@@ -72746,7 +72697,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="60"/>
       <c r="B57" s="60" t="s">
         <v>890</v>
@@ -72761,7 +72712,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="58" t="s">
         <v>878</v>
       </c>
@@ -72778,7 +72729,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="59" t="s">
         <v>881</v>
       </c>
@@ -72795,7 +72746,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="60"/>
       <c r="B60" s="60" t="s">
         <v>890</v>
@@ -72810,7 +72761,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="60"/>
       <c r="B61" s="60" t="s">
         <v>909</v>
@@ -72825,7 +72776,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="60"/>
       <c r="B62" s="60" t="s">
         <v>909</v>
@@ -72840,7 +72791,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="60"/>
       <c r="B63" s="60" t="s">
         <v>909</v>
@@ -72855,7 +72806,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="60"/>
       <c r="B64" s="60" t="s">
         <v>909</v>
@@ -72870,7 +72821,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="60"/>
       <c r="B65" s="60" t="s">
         <v>933</v>
@@ -72885,7 +72836,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="58" t="s">
         <v>879</v>
       </c>
@@ -72902,7 +72853,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="7.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5" ht="7.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="58" t="s">
         <v>879</v>
       </c>
@@ -72935,15 +72886,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2354D58-A693-4C70-9179-E7934BAB386F}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="53.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="53.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="46" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="46" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="46" customWidth="1"/>
-    <col min="4" max="16384" width="53.140625" style="46"/>
+    <col min="1" max="1" width="10.15234375" style="46" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" style="46" customWidth="1"/>
+    <col min="3" max="3" width="21.3828125" style="46" customWidth="1"/>
+    <col min="4" max="16384" width="53.15234375" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="58" t="s">
         <v>869</v>
       </c>
@@ -72954,7 +72905,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>857</v>
       </c>
@@ -72965,7 +72916,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="58" t="s">
         <v>860</v>
       </c>
@@ -72976,7 +72927,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="58" t="s">
         <v>854</v>
       </c>
@@ -72987,7 +72938,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="58" t="s">
         <v>872</v>
       </c>
@@ -72998,7 +72949,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="58" t="s">
         <v>863</v>
       </c>
@@ -73009,7 +72960,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="s">
         <v>866</v>
       </c>
@@ -73020,7 +72971,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="58" t="s">
         <v>875</v>
       </c>
